--- a/data/trans_orig/P25D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35345</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44033</t>
+          <t>45521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16664</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>26164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,34 +1202,34 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11676</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3337</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11369</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>440133</t>
+          <t>441420</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>471967</t>
+          <t>472479</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>418262</t>
+          <t>417876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>434780</t>
+          <t>434299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>866925</t>
+          <t>864118</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>901944</t>
+          <t>902302</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>18852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>897</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>402457</t>
+          <t>402976</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>427670</t>
+          <t>429230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>345134</t>
+          <t>344659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>362933</t>
+          <t>362643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>754169</t>
+          <t>755743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>785263</t>
+          <t>787361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>34029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -2659,97 +2659,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14409</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>13087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>5021</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>12384</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>5021</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>12817</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>517142</t>
+          <t>498119</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>585262</t>
+          <t>558773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>138724</t>
+          <t>157655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621163</t>
+          <t>623370</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148329</t>
+          <t>147712</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>158890</t>
+          <t>158431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228799</t>
+          <t>253152</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>775647</t>
+          <t>774741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53346</t>
+          <t>52601</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13755</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>81774</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,77 +3356,77 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>6266</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>12618</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>14959</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>8062</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>25249</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>6266</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>13194</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>14959</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>7917</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>25308</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8920</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37561</t>
+          <t>35134</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,82 +3469,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>11886</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>4567</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>24440</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>29816</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>16376</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>50451</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>11886</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>4084</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>25016</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>29816</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>17027</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>50500</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>34972</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>916792</t>
+          <t>919392</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>967798</t>
+          <t>964556</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>895350</t>
+          <t>898232</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>944747</t>
+          <t>946921</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1827223</t>
+          <t>1829660</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1907968</t>
+          <t>1909215</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30741</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32622</t>
+          <t>33914</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>29133</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>55355</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>15877</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>42657</t>
+          <t>47108</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>523</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>34644</t>
+          <t>35381</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39864</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>411573</t>
+          <t>411079</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>443916</t>
+          <t>444813</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>777846</t>
+          <t>774220</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>810297</t>
+          <t>809020</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1200209</t>
+          <t>1200756</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1247592</t>
+          <t>1250099</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>27056</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>54556</t>
+          <t>54644</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>17707</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>23389</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18547</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>203732</t>
+          <t>202232</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>233070</t>
+          <t>232391</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>695861</t>
+          <t>696821</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>727576</t>
+          <t>728539</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>911719</t>
+          <t>913311</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>954869</t>
+          <t>954052</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>82233</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>140013</t>
+          <t>139693</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>84529</t>
+          <t>84905</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>128889</t>
+          <t>129490</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>173396</t>
+          <t>178075</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>250695</t>
+          <t>254319</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>36629</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>69075</t>
+          <t>71317</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27452</t>
+          <t>27342</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>59354</t>
+          <t>61092</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>68857</t>
+          <t>69726</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>113798</t>
+          <t>114631</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>52272</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>23740</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>15198</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>35491</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>23740</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>36636</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>42754</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>78645</t>
+          <t>79733</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>58574</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>36944</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>42264</t>
+          <t>41620</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>86058</t>
+          <t>85492</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>969700</t>
+          <t>1166512</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>34300</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1239030</t>
+          <t>1139272</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2201704</t>
+          <t>2040992</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3105991</t>
+          <t>3102308</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3329958</t>
+          <t>3328564</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3403283</t>
+          <t>3403362</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5360009</t>
+          <t>5410842</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>6474138</t>
+          <t>6480554</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11242</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>34633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>28691</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45521</t>
+          <t>42629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,67 +873,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>15026</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>23717</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>12188</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>7292</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>19445</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26164</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>26210</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1064,69 +1064,69 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>17183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4854</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>919</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>459170</t>
+          <t>500713</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>441420</t>
+          <t>479908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>472479</t>
+          <t>513022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>427486</t>
+          <t>467608</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>417876</t>
+          <t>457269</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>434299</t>
+          <t>474682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>886656</t>
+          <t>968321</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>864118</t>
+          <t>947161</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902302</t>
+          <t>983756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>504255</t>
+          <t>549682</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>504255</t>
+          <t>549682</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>504255</t>
+          <t>549682</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>446607</t>
+          <t>487513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>950862</t>
+          <t>1037195</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>950862</t>
+          <t>1037195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>950862</t>
+          <t>1037195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,67 +1520,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>18586</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12078</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>28593</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>2,86%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>16865</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11086</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>25950</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33037</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>25407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>21639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>632</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>132</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>417650</t>
+          <t>445138</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>402976</t>
+          <t>429064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>429230</t>
+          <t>456197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>354693</t>
+          <t>391804</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>344659</t>
+          <t>381437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>362643</t>
+          <t>401406</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>772343</t>
+          <t>836942</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>755743</t>
+          <t>819378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>787361</t>
+          <t>851136</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>450066</t>
+          <t>481012</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450066</t>
+          <t>481012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>450066</t>
+          <t>481012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>381929</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381929</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381929</t>
+          <t>422434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>831995</t>
+          <t>903446</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>831995</t>
+          <t>903446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>831995</t>
+          <t>903446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34029</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>498119</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>245913</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>558773</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>390711</t>
+          <t>436365</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157655</t>
+          <t>422581</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>623370</t>
+          <t>446503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>153905</t>
+          <t>172150</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147712</t>
+          <t>163804</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>158431</t>
+          <t>177432</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>544615</t>
+          <t>608514</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>253152</t>
+          <t>593704</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>774741</t>
+          <t>620879</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>166319</t>
+          <t>186829</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>166319</t>
+          <t>186829</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>166319</t>
+          <t>186829</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>834582</t>
+          <t>658440</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>834582</t>
+          <t>658440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>834582</t>
+          <t>658440</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>37349</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52601</t>
+          <t>56757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>31714</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>61029</t>
+          <t>69063</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40073</t>
+          <t>52559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81774</t>
+          <t>88684</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3223,102 +3223,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>9944</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>5481</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>15974</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>27176</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>18274</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>41600</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>9496</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>4122</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>16073</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>23624</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>14620</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>37861</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17468</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>19937</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35134</t>
+          <t>35866</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>29816</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>50451</t>
+          <t>50836</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>27324</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>19882</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34972</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>944168</t>
+          <t>1027988</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>919392</t>
+          <t>999245</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>964556</t>
+          <t>1050441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>918332</t>
+          <t>791018</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>898232</t>
+          <t>774464</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>946921</t>
+          <t>803982</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1862500</t>
+          <t>1819005</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1829660</t>
+          <t>1787542</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1909215</t>
+          <t>1847360</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1031751</t>
+          <t>1128635</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1031751</t>
+          <t>1128635</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1031751</t>
+          <t>1128635</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>975431</t>
+          <t>858373</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>975431</t>
+          <t>858373</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>975431</t>
+          <t>858373</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2007181</t>
+          <t>1987007</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2007181</t>
+          <t>1987007</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2007181</t>
+          <t>1987007</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>35153</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33914</t>
+          <t>33656</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>46966</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>35546</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>60954</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15877</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>25104</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>15336</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>47108</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35381</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>996</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>432062</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>411079</t>
+          <t>500012</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>444813</t>
+          <t>532391</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>796623</t>
+          <t>786194</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>774220</t>
+          <t>773686</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>809020</t>
+          <t>796525</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1228685</t>
+          <t>1304222</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1200756</t>
+          <t>1281669</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1250099</t>
+          <t>1321724</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>472940</t>
+          <t>565784</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>472940</t>
+          <t>565784</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>472940</t>
+          <t>565784</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>840096</t>
+          <t>829473</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>840096</t>
+          <t>829473</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>840096</t>
+          <t>829473</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1313036</t>
+          <t>1395257</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1313036</t>
+          <t>1395257</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1313036</t>
+          <t>1395257</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>27792</t>
+          <t>24338</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>27181</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>39689</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>37175</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>26207</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>57705</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>10751</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,22 +4961,22 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>814</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>14184</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>23389</t>
+          <t>21711</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16674</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>222635</t>
+          <t>220757</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>202232</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>232391</t>
+          <t>230555</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>714178</t>
+          <t>794240</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>696821</t>
+          <t>776917</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>728539</t>
+          <t>807714</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>936813</t>
+          <t>1014997</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>913311</t>
+          <t>992598</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>954052</t>
+          <t>1032681</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1000160</t>
+          <t>1079720</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1000160</t>
+          <t>1079720</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1000160</t>
+          <t>1079720</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>108440</t>
+          <t>115432</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>81119</t>
+          <t>95249</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>139693</t>
+          <t>148093</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>105862</t>
+          <t>118292</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>84905</t>
+          <t>99495</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>129490</t>
+          <t>142439</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>214303</t>
+          <t>233724</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>178075</t>
+          <t>204238</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>254319</t>
+          <t>270910</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>51381</t>
+          <t>60309</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>36629</t>
+          <t>45302</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>71317</t>
+          <t>80216</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27342</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>61092</t>
+          <t>46911</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>95264</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>69726</t>
+          <t>78852</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>114631</t>
+          <t>119606</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>26761</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>56442</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>37763</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>58268</t>
+          <t>65763</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>42754</t>
+          <t>49361</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>79733</t>
+          <t>87251</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>36969</t>
+          <t>43500</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>21538</t>
+          <t>28428</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>59538</t>
+          <t>64505</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>41143</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>59814</t>
+          <t>69784</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>41620</t>
+          <t>50691</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>85492</t>
+          <t>95682</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>268993</t>
+          <t>24808</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1166512</t>
+          <t>45561</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>27421</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>284185</t>
+          <t>44531</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>29483</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1139272</t>
+          <t>66320</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2866396</t>
+          <t>3148987</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2040992</t>
+          <t>3108848</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3102308</t>
+          <t>3183012</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3365217</t>
+          <t>3403013</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3328564</t>
+          <t>3371360</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3403362</t>
+          <t>3428626</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>6231613</t>
+          <t>6552001</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5410842</t>
+          <t>6502649</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>6480554</t>
+          <t>6598573</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3366707</t>
+          <t>3432854</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>3366707</t>
+          <t>3432854</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3366707</t>
+          <t>3432854</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3571110</t>
+          <t>3628211</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3571110</t>
+          <t>3628211</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3571110</t>
+          <t>3628211</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>6937817</t>
+          <t>7061066</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6937817</t>
+          <t>7061066</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6937817</t>
+          <t>7061066</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
